--- a/data/manual/欠場管理リスト.xlsx
+++ b/data/manual/欠場管理リスト.xlsx
@@ -8,21 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dev_tomo/Desktop/tt_prj_restart/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D882C0AD-1B7B-B94E-8A85-20B8F51809BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB167DC-56BD-ED4F-9B66-FE86E01CF01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="2120" windowWidth="27900" windowHeight="16940" xr2:uid="{4D8BCF16-C3F5-FF40-8C4E-B4DEA8317F2D}"/>
+    <workbookView xWindow="1800" yWindow="1380" windowWidth="27220" windowHeight="17920" xr2:uid="{4D8BCF16-C3F5-FF40-8C4E-B4DEA8317F2D}"/>
   </bookViews>
   <sheets>
     <sheet name="欠場管理" sheetId="1" r:id="rId1"/>
     <sheet name="判断目安" sheetId="2" r:id="rId2"/>
     <sheet name="設定" sheetId="3" r:id="rId3"/>
+    <sheet name="ドロップダウンリスト" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="588">
   <si>
     <t>round_start</t>
   </si>
@@ -93,10 +107,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ヴァンフォーレ甲府</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>松本山雅FC</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -105,10 +115,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>名古屋グランパス</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>右ハムストリング肉離れ</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -117,27 +123,15 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ガンバ大阪</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>左ハムストリング肉離れ、左ヒラメ筋肉離れ</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>RB大宮アルディージャ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>左大腿二頭筋肉離れ</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
     <t>右大腿二頭筋肉離れ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>栃木SC</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -188,15 +182,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ブラウブリッツ秋田</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>右ハムストリングス肉離れ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>湘南ベルマーレ</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -228,10 +214,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>サンフレッチェ広島</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>左ヒラメ筋損傷による治療のためドイツへ一時帰国した</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -247,10 +229,6 @@
     <t>スプリント、切り返し、後半の走力維持、に直結。
 FW・WG・SBなら影響大、
 一度復帰しても数節後に再発可能性</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>セレッソ大阪</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -482,10 +460,6 @@
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFAtZW04b1VnQ3F6T2xfV2tkMmtWMEJldTBnNjg5bTlUWTd4QWZvTktObno2YWQtYkdQRGV5TTUyY3IxNEZWeHVWdll1VzBmUkg4OHg1Z2poQlI?oc=5</t>
-  </si>
-  <si>
-    <t>藤枝MYFC</t>
-    <phoneticPr fontId="18"/>
   </si>
   <si>
     <r>
@@ -543,10 +517,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>コンサドーレ札幌</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>マリオセルジオ</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -578,10 +548,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ヴィッセル神戸</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>右鎖骨粉砕骨折</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -594,43 +560,1881 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ジュビロ磐田</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>ガブリエルゴメス</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
+    <t>山川哲史</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>カード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>原田亘</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>鳥海芳樹</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>小島幹敏</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アマドゥバカヨコ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>見木友哉</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左膝後十字靭帯不全、外側半月板損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>外側半月板損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>手術をしない場合：約1ヶ月〜3ヶ月</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>手術をした場合：約2ヶ月〜3ヶ月　or　約6ヶ月〜9ヶ月</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左大腿二頭筋断裂</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右ヒラメ筋肉離れで全治約8週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左大腿二頭筋肉離れで全治約8週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>8節</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レノファ山口FC</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右肩腱板断裂、右肩反復性肩関節脱臼の手術を行い、術後6ヶ月程度の加療予定</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右ヒラメ筋損傷、右腓腹筋損傷で全治約6～8週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>FC大阪</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>反復性肩関節脱臼で全治約4ヶ月</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>中村桐耶</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t xml:space="preserve">高宇洋 </t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>曽田一騎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岩本翔</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>沼田航征</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>野澤陸</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>吉田源太郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>高橋祥平</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>富澤雅也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右大腿四頭筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Ⅰ度（軽度）：1〜2週間
+Ⅱ度（中等度）：4〜8週間
+Ⅲ度（重度）：3ヶ月以上</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右鎖骨下静脈血栓症、右胸郭出口症候群</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>病気</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ビョウキ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>FC琉球</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左ヒラメ筋肉離れで全治約8週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左肘肘関節脱臼で全治約8週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スタチオーリミケーレ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左大腿二頭筋損傷で全治約8～10週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>フォファナマリック</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>森重真人</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>山市秀翔</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>鈴木順也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>近藤優成</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t xml:space="preserve">辻岡佑真	</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左大腿直筋腱断裂</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>「走る」
+軽度（Ⅰ度：筋線維の微細損傷）：2週〜3週間
+中等度（Ⅱ度：部分断裂）：1ヶ月〜3ヶ月
+重度（Ⅲ度：完全断裂）：4ヶ月〜6ヶ月以上</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">ハシル </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>「蹴る」
+保存療法（手術なし）: 競技復帰まで 12週間〜15週間（約3〜4ヶ月）
+手術（腱縫合）: 競技復帰まで 20週間〜30週間（約5〜7ヶ月）</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">ケル </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>20節</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木寺優直</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コンディション不良</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イェンギクシニ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>J1（2026）推奨チーム名</t>
+  </si>
+  <si>
+    <t>FC東京</t>
+  </si>
+  <si>
+    <t>京都</t>
+  </si>
+  <si>
+    <t>千葉</t>
+  </si>
+  <si>
+    <t>名古屋</t>
+  </si>
+  <si>
+    <t>岡山</t>
+  </si>
+  <si>
+    <t>川崎Ｆ</t>
+  </si>
+  <si>
+    <t>広島</t>
+  </si>
+  <si>
+    <t>東京Ｖ</t>
+  </si>
+  <si>
+    <t>柏</t>
+  </si>
+  <si>
+    <t>横浜FM</t>
+  </si>
+  <si>
+    <t>水戸</t>
+  </si>
+  <si>
+    <t>浦和</t>
+  </si>
+  <si>
+    <t>清水</t>
+  </si>
+  <si>
+    <t>町田</t>
+  </si>
+  <si>
+    <t>神戸</t>
+  </si>
+  <si>
+    <t>福岡</t>
+  </si>
+  <si>
+    <t>長崎</t>
+  </si>
+  <si>
+    <t>鹿島</t>
+  </si>
+  <si>
+    <t>Ｃ大阪</t>
+  </si>
+  <si>
+    <t>Ｇ大阪</t>
+  </si>
+  <si>
+    <t>J2（2026）推奨チーム名</t>
+  </si>
+  <si>
+    <t>いわき</t>
+  </si>
+  <si>
     <t>今治</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>山川哲史</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>神戸</t>
-    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>仙台</t>
+  </si>
+  <si>
+    <t>八戸</t>
+  </si>
+  <si>
+    <t>大分</t>
+  </si>
+  <si>
+    <t>大宮</t>
+  </si>
+  <si>
+    <t>宮崎</t>
+  </si>
+  <si>
+    <t>富山</t>
+  </si>
+  <si>
+    <t>山形</t>
+  </si>
+  <si>
+    <t>徳島</t>
+  </si>
+  <si>
+    <t>新潟</t>
+  </si>
+  <si>
+    <t>札幌</t>
+  </si>
+  <si>
+    <t>栃木Ｃ</t>
+  </si>
+  <si>
+    <t>横浜FC</t>
+  </si>
+  <si>
+    <t>湘南</t>
+  </si>
+  <si>
+    <t>甲府</t>
+  </si>
+  <si>
+    <t>磐田</t>
+  </si>
+  <si>
+    <t>秋田</t>
+  </si>
+  <si>
+    <t>藤枝</t>
+  </si>
+  <si>
+    <t>鳥栖</t>
+  </si>
+  <si>
+    <t>ドロップダウン用正式名</t>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">ヨウ </t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t xml:space="preserve">セイシキメイ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右膝前十字靭帯損傷、内側側副靭帯損傷、外側半月板損傷、大腿骨外顆骨挫傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左膝前十字靭帯損傷、外側半月板損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左ハムストリングス肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右大腿直筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>パトリッキヴェロン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右脛骨骨挫傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左足関節骨挫傷で全治4週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ロアッソ熊本</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右第3中手指骨骨折で加療期間は手術日より約8週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左長内転筋付着部炎、恥骨骨挫傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>第5腰椎分離症</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>奈良クラブ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左第5中足骨骨折で全治約4ヶ月</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>前下脛腓靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>脛骨骨挫傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>骨の打撲（骨の内部にダメージがある状態）**で、骨折より軽い</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>恥骨骨挫傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>股関節・体幹・キック動作すべてに関わる</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>内ももの筋肉（長内転筋）が恥骨にくっつく部分の炎症</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左長内転筋付着部炎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>腰椎分離症</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>中等度（分離進行）2〜4ヶ月がメインゾーン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>16節</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>中等度（部分断裂）4〜8週間が 一番多いゾーン、3〜6試合欠場</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>中等度（Ⅱ度：部分断裂）3〜6週間、一番多い、2〜5試合欠場</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>5 節</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大腿直筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>藤山智史</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>畑橋拓輝</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>長谷川巧</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>浦上仁騎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>佐藤碧</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>永井颯太</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>舘幸希</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>島谷義進</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>一村聖連</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>佐々木旭</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大関友翔</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>中村亮太朗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>渡邊啓吾</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>安田虎士朗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キムテウォン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>布施谷翔</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>小塚和季</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ジョアンペドロ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>井手口陽介</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>五十嵐太陽</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左股関節唇損傷で復帰まで約3ヶ月を要する見込み</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左ヒラメ筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ヒラメ筋肉離れ</t>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">ニクバナレ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>清武弘嗣</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>北村海チディ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左足第五中足骨疲労骨折で全治約12週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>内藤大和</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右足関節三角靭帯損傷、前距腓靱帯損傷、前脛腓靭帯損傷で全治約4週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>小出悠太</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左足関節三角靭帯損傷、前脛腓靭帯損傷、骨間膜損傷で全治約4週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>栃木SC</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大腿直筋筋損傷で復帰まで8週を要する見込み</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>鈴木俊也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>加藤千尋</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左ヒラメ筋肉離れで加療期間は受傷日より約4週間</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>松本山雅FC</t>
+  </si>
+  <si>
+    <t>左大腿二頭筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イコール　ハムストリング肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ガイナーレ鳥取</t>
+  </si>
+  <si>
+    <t>右アキレス腱断裂</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右距骨離断性骨軟骨炎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アキレス腱断裂</t>
+  </si>
+  <si>
+    <t>6ヶ月 〜 10ヶ月、25節 〜 全試合、ほぼシーズン終了</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>保存療法（軽症）：3ヶ月前後10〜12節</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>手術（一般的）：4ヶ月〜6ヶ月15〜25節</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>15節</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>谷口栄斗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>伊藤颯真</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>渋谷諒太</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>吉田伊吹</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>香取潤</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>J1百年構想(f)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第９節第１日(04/04)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第９節第２日(04/05)</t>
+  </si>
+  <si>
+    <t>J2/J3百年構想(f)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第８節第２日(03/29)</t>
+  </si>
+  <si>
+    <t>J2/J3百年構想(a)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第８節第１日(03/28)</t>
+  </si>
+  <si>
+    <t>相模原</t>
+  </si>
+  <si>
+    <t>大森渚生</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大森博</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>西村真祈</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>城和隼颯</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>新保海鈴</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>竹内崇人</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マルクスヴィニシウス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左脛骨内果骨折</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約４〜6カ月</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヤク </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>24節</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>左膝前十字靭帯損傷、左膝外側半月板損傷で加療期間は手術日より約9ヶ月</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右アキレス腱断裂で全治6ヶ月の見込み</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>武者大夢</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>遠野大弥</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t xml:space="preserve">森田　大智 - </t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>AC長野パルセイロ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右内側側副靱帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレードI（軽症）靭帯が伸びた状態（微細損傷）約1〜3週間
+グレードII（中等症）靭帯の一部が切れている約4〜8週間（1〜2ヶ月）
+グレードIII（重症）靭帯が完全に断裂している約2〜3ヶ月以上</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左第2趾基節骨骨折で全治約6週</t>
+  </si>
+  <si>
+    <t>ギラヴァンツ北九州</t>
+  </si>
+  <si>
+    <t>平松昇</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>加藤玄</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紺野和也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木實快斗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>長倉幹樹</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右大腿二頭筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大腿二頭筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Ⅰ型（軽症）　筋膜の損傷・出血のみ（微細損傷）　約1〜2週間
+Ⅱ型（中等症）　腱膜（筋肉の膜）の損傷　約4〜8週間（1〜2ヶ月）
+Ⅲ型（重症）　腱の断裂や骨からの剥離　約3ヶ月以上（要手術も）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左ヒラメ筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右内転筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左ハムストリング肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>エリキ</t>
+  </si>
+  <si>
+    <t>J1百年構想(b)</t>
+  </si>
+  <si>
+    <t>橋本拳人</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マテウストゥーレル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>長野</t>
+  </si>
+  <si>
+    <t>J2/J3百年構想(b)</t>
+  </si>
+  <si>
+    <t>金沢</t>
+  </si>
+  <si>
+    <t>北九州</t>
+  </si>
+  <si>
+    <t>杉山耀建</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>高橋勇利也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>行德瑛</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>松本大輔</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>井澤春輝</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右肩関節脱臼</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>保存療法（手術なし）の場合：約1.5ヶ月〜2ヶ月
+欠場節数の目安： 約6節〜10節前後</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右肩関節脱臼</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>7節</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右足関節遊離体</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右足関節遊離体</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>通称「関節ねずみ」
+標準的な復帰の場合（約2ヶ月〜）： 約8〜10節</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9節</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右肘関節靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>GKのケガ。欠場節の予想：約4週〜8週（1ヶ月〜2ヶ月）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右肘関節靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右膝前十字靱帯損傷、右膝外側半月板損傷で全治6ヶ月程度を要する見込み</t>
+  </si>
+  <si>
+    <t>公式 左ハムストリング肉離れで加療期間は受傷日より約4週間</t>
+  </si>
+  <si>
+    <t>FC琉球</t>
+  </si>
+  <si>
+    <t>ロアッソ熊本</t>
+  </si>
+  <si>
+    <t>清水祐輔</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>内田瑞己</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>福井光輝</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>藤春廣輝</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>長嶋志歩</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>柴田壮介</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ダニーロ</t>
+  </si>
+  <si>
+    <t>J1百年構想(a)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１０節第１日(04/11)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１０節第１日(04/11)</t>
+  </si>
+  <si>
+    <t>イスマイラ</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１節第４日(04/08)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１０節第１日(04/12)</t>
+  </si>
+  <si>
+    <t>群馬</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１０節第２日(04/12)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Bグループ第１０節第２日(04/12)</t>
+  </si>
+  <si>
+    <t>熊本</t>
   </si>
   <si>
     <t>カード</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>原田亘</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>柏</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>鳥海芳樹</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>水戸</t>
+  </si>
+  <si>
+    <t>岡村大八</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ジェイソンキニョーネス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>住吉ジェラニレショーン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>須貝英大</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>本間至恩</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>田代雅也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>安野匠</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>諸岡裕人</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>野瀬翔也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岩武克弥</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>神山京右</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岩下航</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 腰椎椎間板ヘルニアで加療期間は手術日より約3ヶ月</t>
+  </si>
+  <si>
+    <t>徳島ヴォルティス</t>
+  </si>
+  <si>
+    <t>小林悠</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>佐藤瑶大</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大西遼太郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>冨永虹七</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>三井大輝</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左眼窩底骨折</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>眼窩底骨折</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約4週〜8週（1ヶ月〜2ヶ月）
+　・保存療法（手術なし）の場合：約4週間（4〜5節）
+　・手術を行う場合：約6〜8週間（6〜10節以上）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右膝蓋骨骨折及び右膝蓋腱部分断裂</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>欠場節の予想：今季絶望の可能性が高い（全治6ヶ月〜8ヶ月以上）</t>
+  </si>
+  <si>
+    <t>28節</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右膝外側半月板断裂</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右膝外側半月板断裂</t>
+  </si>
+  <si>
+    <t>・切除術（傷んだ部分を切り取る）の場合：約2ヶ月〜3ヶ月
+　欠場節数の目安：約8節〜12節
+・縫合術（傷んだ部分を縫い合わせる）の場合：約5ヶ月〜7ヶ月
+　欠場節数の目安：約20節〜25節（今季絶望に近い）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１１節第２日(04/18)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１１節第２日(04/18)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１１節第１日(04/18)</t>
+  </si>
+  <si>
+    <t>栃木SC</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１１節第２日(04/19)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Aグループ第１１節第２日(04/18)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１１節第１日(04/18)</t>
+  </si>
+  <si>
+    <t>公式 右大腿二頭筋肉離れ</t>
+  </si>
+  <si>
+    <t>新井悠太</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>染野唯月</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>宮原和也</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アレックスソウザ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>荒木駿太</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岩﨑博</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ペドロアウグスト</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>髙江麗央</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>嶋田慎太郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>松木駿之介</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左大腿二頭筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左ハムストリング損傷で全治8週</t>
+  </si>
+  <si>
+    <t>公式 左ヒラメ筋肉離れで全治6週</t>
+  </si>
+  <si>
+    <t>公式 左ハムストリング肉離れで全治8週</t>
+  </si>
+  <si>
+    <t>ジョー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右膝内側側副靱帯損傷、右足関節靭帯損傷で復帰まで6〜8週を要する見込み</t>
+  </si>
+  <si>
+    <t>公式 左ハムストリング筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>佐藤陽成</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>福森晃斗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>上原牧人</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>塩浜遼</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>青島太一</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>阪田澪哉</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左頬骨骨折、左眼窩底骨折で全治は手術日から約1～2ヶ月</t>
+  </si>
+  <si>
+    <t>一瀬大寿</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１２節第２日(04/25)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１２節第１日(04/24)</t>
+  </si>
+  <si>
+    <t>マテウスサヴィオ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>前貴之</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>久保藤次郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１３節第１日(04/29)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１７節第１日(04/22)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１２節第１日(04/25)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１２節第２日(04/26)</t>
+  </si>
+  <si>
+    <t>岐阜</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１２節第１日(04/25)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Bグループ第１２節第１日(04/25</t>
+  </si>
+  <si>
+    <t>エンリケトレヴィザン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>重見柾斗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>奈良竜樹</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ディエゴピトゥカ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>牧野虎太郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>中村駿</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木許太賀</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右ハムストリング肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左肘内側側副靭帯損傷および橈骨頭骨折で全治2ヶ月程度を要する見込み</t>
+  </si>
+  <si>
+    <t>公式 右足関節外側靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>山越康平</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>加藤有輝</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>関節外側靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレードI（軽症）	　　約2〜4週間
+グレードII（中等症）　約6〜10週間（1.5〜2.5ヶ月）
+グレードIII（重症）　　約3〜6ヶ月以上（手術検討）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ツエーゲン金沢</t>
+  </si>
+  <si>
+    <t>松岡瑠夢</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左膝内側側副靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>内側側副靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>手術は稀: 前十字靭帯（ACL）とは違い、単独損傷であればプロ選手でも**保存療法（リハビリ）**で治すのが標準的</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右腓腹筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右腓腹筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ふくらはぎ
+Ⅰ型（軽症）	筋細胞の微細損傷・出血	約1〜2週間
+Ⅱ型（中等症）	部分断裂（筋肉と腱の境界部が多い）	約4〜6週間
+Ⅲ型（重症）	完全断裂または広範囲な損傷	約2〜3ヶ月以上</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左膝内側側副靱帯損傷</t>
+  </si>
+  <si>
+    <t>公式 左手舟状骨骨折で加療期間は手術日より約8週間</t>
+  </si>
+  <si>
+    <t>ザスパ群馬</t>
+  </si>
+  <si>
+    <t>加々美登生</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>安藤一哉</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左大腿二頭筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左膝前十字靱帯損傷、外側半月板損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>半田陸</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右胸郭出口症候群で全治3か月程度要する見込み(手術日より)</t>
+  </si>
+  <si>
+    <t>川崎Ｆ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>家長昭博</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 下腿三頭筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>熊本雄太</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>下腿三頭筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>腓腹筋・ヒラメ筋を含む。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スパチョーク</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右膝内側側副靱帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左内側半月板損傷で全治約4ヶ月の見込み</t>
+  </si>
+  <si>
+    <t>貫真郷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>シルヴァンデランド</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>松村晟怜</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風間宏希</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>小野裕二</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右腓腹筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右手舟状骨骨折</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>右手舟状骨骨折</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ギプス固定だけでも1ヶ月〜2ヶ月近く。
+手術の選択： 早期復帰を目指すJリーガーの場合、全治2〜3ヶ月、あるいはそれ以上</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10節</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">セツ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右足関節前距腓靱帯損傷、前下脛腓靱帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左ハムストリングス損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>トレーニングマッチで負傷した。城福監督「そんなにすぐ戻ってこれるような状況ではない」</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>山見大登</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１３節第１日(04/29)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１３節第１日(04/29)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１３節第１日(04/29)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Aグループ第１３節第１日(04/29)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Bグループ第１３節第１日(04/29)</t>
+  </si>
+  <si>
+    <t>津久井佳祐</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>柴戸海</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>小泉佳穂</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大畑歩夢</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岡﨑亮平</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>堤陽輝</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>永野修都</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>荒木大吾</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>宮崎純真</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１４節第２日(05/03)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１４節第１日(05/02)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１４節第２日(05/03)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１４節第２日(05/03)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１４節第１日(05/02)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１４節第１日(05/02)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１４節第２日(05/03)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Aグループ第１４節第２日(05/03)</t>
+  </si>
+  <si>
+    <t>カイケ</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Aグループ第１４節第１日(05/02)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Bグループ第１４節第２日(05/03)</t>
+  </si>
+  <si>
+    <t>琉球</t>
+  </si>
+  <si>
+    <t>温井駿斗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右アキレス腱断裂</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右膝内側側副靱帯損傷で復帰まで10〜12週を要する見込み</t>
+  </si>
+  <si>
+    <t>バングーナガンデ佳史扶</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大腿二頭筋損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ハムストリングスの肉離れ
+</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 右膝関節軟骨損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>膝関節軟骨損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>軽度の洗浄術（クリーニング）なら数ヶ月ですが、軟骨を修復・移植する手術（自己軟骨移植など）を行った場合、復帰までに半年から1年以上かかることも</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左大腿直筋肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岡野凜平</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>三竿健斗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>名古新太郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>高吉正真</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>松井蓮之</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>西村慧祐</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>堂鼻起暉</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>荒木翔</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ジェイソンゲリア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>甲斐健太郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>池田廉</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>西野太陽</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>扇原貴宏</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１５節第１日(05/06)</t>
+  </si>
+  <si>
+    <t>エリソン</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１５節第１日(05/06)</t>
+  </si>
+  <si>
+    <t>福島</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１５節第１日(05/06)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１５節第１日(05/06)</t>
+  </si>
+  <si>
+    <t>松本</t>
+  </si>
+  <si>
+    <t>FC大阪</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Aグループ第１５節第１日(05/06)</t>
+  </si>
+  <si>
+    <t>山口</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Bグループ第１５節第１日(05/06)</t>
+  </si>
+  <si>
+    <t>讃岐</t>
+  </si>
+  <si>
+    <t>高知</t>
+  </si>
+  <si>
+    <t>林幸多郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グスタボバヘット</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>新井直人</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>芦部晃生</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>山内琳太郎</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>加藤拓己</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>文仁柱</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>久保吏久斗</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>輪笠祐士</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>田尾佳祐</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>トニーアンデルソン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>小林大智</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>吉田泰授</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左膝前十字靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>手術（再建術）	プロ選手や競技復帰を望む場合	約8ヶ月 〜 10ヶ月
+保存療法（リハビリ）	部分断裂で強度が保たれている場合	約3ヶ月 〜 6ヶ月</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>前十字靭帯損傷</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">マエ </t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>後十字靭帯損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>膝の後方にある靭帯ですが、こちらは前十字に比べると血流が少しあり、保存療法で治せるケースも多いです。
+軽度〜中等度: 約2ヶ月 〜 4ヶ月
+重度（手術の場合）: 約6ヶ月 〜 9ヶ月以上</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左膝複合靭帯損傷、半月板損傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>才藤龍治</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>公式 左ハムストリングス肉離れ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　EASTグループ第１６節第１日(05/09)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ１百年構想リーグ　WESTグループ第１６節第２日(05/10)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１６節第２日(05/10)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１６節第１日(05/09)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Aグループ第１６節第１日(05/09)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　WEST-Aグループ第１６節第２日(05/10)</t>
+  </si>
+  <si>
+    <t>明治安田Ｊ２・Ｊ３百年構想リーグ　EAST-Bグループ第１６節第２日(05/10)</t>
+  </si>
+  <si>
+    <t>牛澤健</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岡哲平</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>柳育崇</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マテイヨニッチ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アルトゥールシルバ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>福井啓太</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>奥村仁</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>チョンウヨン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>森侑里</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>岩尾憲</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ルーカスバルセロス</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -642,7 +2446,7 @@
     <numFmt numFmtId="176" formatCode="m/d;@"/>
     <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="34">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -867,8 +2671,50 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="-webkit-standard"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1078,8 +2924,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1207,6 +3071,26 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1341,7 +3225,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1377,19 +3261,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1428,6 +3300,102 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="40" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="40" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1806,56 +3774,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24B5C67-964E-DB46-9987-021F3DCE0991}">
-  <dimension ref="A1:AF28"/>
+  <sheetPr>
+    <tabColor theme="7"/>
+  </sheetPr>
+  <dimension ref="A1:AF239"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="12" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" style="9" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="3"/>
     <col min="4" max="4" width="7.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" style="3" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="27.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14" style="25" customWidth="1"/>
+    <col min="8" max="8" width="39.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" style="21" customWidth="1"/>
     <col min="10" max="10" width="13.7109375" style="3" customWidth="1"/>
     <col min="11" max="11" width="46.7109375" style="3" customWidth="1"/>
     <col min="12" max="12" width="10.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="27" customFormat="1" ht="104" customHeight="1">
+    <row r="1" spans="1:11" s="23" customFormat="1" ht="104" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>75</v>
+      <c r="I1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1">
@@ -1863,13 +3834,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>1</v>
@@ -1883,14 +3854,14 @@
       <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>74</v>
+      <c r="I2" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1907,13 +3878,13 @@
         <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>9</v>
@@ -1933,16 +3904,16 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1959,16 +3930,16 @@
         <v>5</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1985,16 +3956,16 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2011,16 +3982,16 @@
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2037,16 +4008,16 @@
         <v>5</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2063,16 +4034,16 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2089,16 +4060,16 @@
         <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2115,16 +4086,16 @@
         <v>5</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2141,16 +4112,16 @@
         <v>12</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>96</v>
+        <v>190</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>87</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2167,16 +4138,16 @@
         <v>5</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2193,16 +4164,16 @@
         <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>95</v>
+        <v>161</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>86</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2219,16 +4190,16 @@
         <v>6</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2245,16 +4216,16 @@
         <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -2271,16 +4242,16 @@
         <v>12</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2297,16 +4268,16 @@
         <v>5</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:32">
@@ -2323,16 +4294,16 @@
         <v>5</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:32">
@@ -2349,25 +4320,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="25">
+        <v>17</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="21">
         <v>46075</v>
       </c>
-      <c r="J20" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>71</v>
+      <c r="J20" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:32">
@@ -2384,47 +4355,47 @@
         <v>10</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="30">
+      <c r="I21" s="26">
         <v>46076.75277777778</v>
       </c>
-      <c r="J21" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="K21" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
-      <c r="AE21" s="20"/>
-      <c r="AF21" s="20"/>
+      <c r="J21" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K21" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16"/>
     </row>
     <row r="22" spans="1:32">
       <c r="A22" s="3">
@@ -2440,19 +4411,19 @@
         <v>8</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -2469,16 +4440,16 @@
         <v>12</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:32">
@@ -2495,16 +4466,16 @@
         <v>14</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:32">
@@ -2521,13 +4492,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:32">
@@ -2544,13 +4515,13 @@
         <v>1</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:32">
@@ -2567,13 +4538,13 @@
         <v>2</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:32">
@@ -2590,14 +4561,5856 @@
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="A29" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="9">
+        <v>46087</v>
+      </c>
+      <c r="C29" s="3">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="A30" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46087</v>
+      </c>
+      <c r="C30" s="3">
+        <v>5</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="A31" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46087</v>
+      </c>
+      <c r="C31" s="3">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32">
+      <c r="A32" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46081</v>
+      </c>
+      <c r="C32" s="3">
+        <v>5</v>
+      </c>
+      <c r="D32" s="3">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46082</v>
+      </c>
+      <c r="C33" s="3">
+        <v>5</v>
+      </c>
+      <c r="D33" s="3">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46082</v>
+      </c>
+      <c r="C34" s="3">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46083</v>
+      </c>
+      <c r="C35" s="3">
+        <v>5</v>
+      </c>
+      <c r="D35" s="3">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46083</v>
+      </c>
+      <c r="C36" s="3">
+        <v>5</v>
+      </c>
+      <c r="D36" s="3">
+        <v>8</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C37" s="3">
+        <v>5</v>
+      </c>
+      <c r="D37" s="3">
+        <v>24</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46085</v>
+      </c>
+      <c r="C38" s="3">
+        <v>5</v>
+      </c>
+      <c r="D38" s="3">
+        <v>8</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46086</v>
+      </c>
+      <c r="C39" s="3">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3">
+        <v>16</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>119</v>
-      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46089</v>
+      </c>
+      <c r="C40" s="3">
+        <v>6</v>
+      </c>
+      <c r="D40" s="3">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46090</v>
+      </c>
+      <c r="C41" s="3">
+        <v>6</v>
+      </c>
+      <c r="D41" s="3">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46090</v>
+      </c>
+      <c r="C42" s="3">
+        <v>6</v>
+      </c>
+      <c r="D42" s="3">
+        <v>20</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46090</v>
+      </c>
+      <c r="C43" s="3">
+        <v>6</v>
+      </c>
+      <c r="D43" s="3">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C44" s="3">
+        <v>6</v>
+      </c>
+      <c r="D44" s="3">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C45" s="3">
+        <v>6</v>
+      </c>
+      <c r="D45" s="3">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46092</v>
+      </c>
+      <c r="C46" s="3">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46092</v>
+      </c>
+      <c r="C47" s="3">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46093</v>
+      </c>
+      <c r="C48" s="3">
+        <v>6</v>
+      </c>
+      <c r="D48" s="3">
+        <v>20</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46094</v>
+      </c>
+      <c r="C49" s="3">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="9">
+        <v>46095</v>
+      </c>
+      <c r="C50" s="3">
+        <v>6</v>
+      </c>
+      <c r="D50" s="3">
+        <v>14</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="9">
+        <v>46095</v>
+      </c>
+      <c r="C51" s="3">
+        <v>6</v>
+      </c>
+      <c r="D51" s="3">
+        <v>12</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B52" s="9">
+        <v>46095</v>
+      </c>
+      <c r="C52" s="3">
+        <v>6</v>
+      </c>
+      <c r="D52" s="3">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B53" s="9">
+        <v>46095</v>
+      </c>
+      <c r="C53" s="3">
+        <v>6</v>
+      </c>
+      <c r="D53" s="3">
+        <v>5</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B54" s="9">
+        <v>46096</v>
+      </c>
+      <c r="C54" s="3">
+        <v>7</v>
+      </c>
+      <c r="D54" s="3">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B55" s="9">
+        <v>46097</v>
+      </c>
+      <c r="C55" s="3">
+        <v>7</v>
+      </c>
+      <c r="D55" s="3">
+        <v>4</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B56" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C56" s="3">
+        <v>7</v>
+      </c>
+      <c r="D56" s="3">
+        <v>9</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B57" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C57" s="3">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3">
+        <v>6</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C58" s="3">
+        <v>7</v>
+      </c>
+      <c r="D58" s="3">
+        <v>16</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B59" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C59" s="3">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>20</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B60" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C60" s="3">
+        <v>7</v>
+      </c>
+      <c r="D60" s="3">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C61" s="3">
+        <v>7</v>
+      </c>
+      <c r="D61" s="3">
+        <v>6</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B62" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C62" s="3">
+        <v>7</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="G62" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B63" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C63" s="3">
+        <v>7</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F63" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="G63" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B64" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C64" s="3">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F64" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="G64" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B65" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C65" s="3">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F65" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="G65" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B66" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C66" s="3">
+        <v>7</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F66" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="G66" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B67" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C67" s="3">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F67" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B68" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C68" s="3">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="G68" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B69" s="9">
+        <v>46100</v>
+      </c>
+      <c r="C69" s="3">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F69" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="G69" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B70" s="9">
+        <v>46102</v>
+      </c>
+      <c r="C70" s="3">
+        <v>8</v>
+      </c>
+      <c r="D70" s="3">
+        <v>12</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I70" s="3"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B71" s="9">
+        <v>46103</v>
+      </c>
+      <c r="C71" s="3">
+        <v>8</v>
+      </c>
+      <c r="D71" s="3">
+        <v>6</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B72" s="9">
+        <v>46104</v>
+      </c>
+      <c r="C72" s="3">
+        <v>8</v>
+      </c>
+      <c r="D72" s="3">
+        <v>12</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B73" s="9">
+        <v>46104</v>
+      </c>
+      <c r="C73" s="3">
+        <v>8</v>
+      </c>
+      <c r="D73" s="3">
+        <v>4</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B74" s="9">
+        <v>46104</v>
+      </c>
+      <c r="C74" s="3">
+        <v>8</v>
+      </c>
+      <c r="D74" s="3">
+        <v>4</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B75" s="9">
+        <v>46104</v>
+      </c>
+      <c r="C75" s="3">
+        <v>8</v>
+      </c>
+      <c r="D75" s="3">
+        <v>8</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B76" s="9">
+        <v>46104</v>
+      </c>
+      <c r="C76" s="3">
+        <v>9</v>
+      </c>
+      <c r="D76" s="3">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B77" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C77" s="3">
+        <v>9</v>
+      </c>
+      <c r="D77" s="3">
+        <v>5</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B78" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C78" s="3">
+        <v>8</v>
+      </c>
+      <c r="D78" s="3">
+        <v>4</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B79" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C79" s="3">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3">
+        <v>5</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B80" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C80" s="3">
+        <v>8</v>
+      </c>
+      <c r="D80" s="3">
+        <v>25</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B81" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C81" s="3">
+        <v>8</v>
+      </c>
+      <c r="D81" s="3">
+        <v>15</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B82" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C82" s="3">
+        <v>9</v>
+      </c>
+      <c r="D82" s="3">
+        <v>24</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" s="39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B83" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C83" s="3">
+        <v>9</v>
+      </c>
+      <c r="D83" s="3">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H83" t="s">
+        <v>276</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B84" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C84" s="3">
+        <v>9</v>
+      </c>
+      <c r="D84" s="3">
+        <v>1</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H84" t="s">
+        <v>277</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B85" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C85" s="3">
+        <v>8</v>
+      </c>
+      <c r="D85" s="3">
+        <v>1</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H85" t="s">
+        <v>279</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B86" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C86" s="3">
+        <v>8</v>
+      </c>
+      <c r="D86" s="3">
+        <v>1</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="G86" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H86" t="s">
+        <v>279</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B87" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C87" s="3">
+        <v>8</v>
+      </c>
+      <c r="D87" s="3">
+        <v>1</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="G87" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H87" t="s">
+        <v>281</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B88" s="9">
+        <v>46106</v>
+      </c>
+      <c r="C88" s="3">
+        <v>8</v>
+      </c>
+      <c r="D88" s="3">
+        <v>1</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="G88" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H88" t="s">
+        <v>279</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B89" s="9">
+        <v>46107</v>
+      </c>
+      <c r="C89" s="3">
+        <v>8</v>
+      </c>
+      <c r="D89" s="3">
+        <v>36</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" s="41" customFormat="1">
+      <c r="A90" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B90" s="40">
+        <v>46107</v>
+      </c>
+      <c r="C90" s="18">
+        <v>9</v>
+      </c>
+      <c r="D90" s="18">
+        <v>24</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="I90" s="20"/>
+      <c r="J90" s="18"/>
+      <c r="K90" s="18"/>
+      <c r="L90" s="18"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B91" s="9">
+        <v>46110</v>
+      </c>
+      <c r="C91" s="3">
+        <v>9</v>
+      </c>
+      <c r="D91" s="3">
+        <v>3</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B92" s="9">
+        <v>46111</v>
+      </c>
+      <c r="C92" s="3">
+        <v>9</v>
+      </c>
+      <c r="D92" s="3">
+        <v>6</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B93" s="9">
+        <v>46111</v>
+      </c>
+      <c r="C93" s="3">
+        <v>9</v>
+      </c>
+      <c r="D93" s="3">
+        <v>5</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B94" s="9">
+        <v>46111</v>
+      </c>
+      <c r="C94" s="3">
+        <v>9</v>
+      </c>
+      <c r="D94" s="3">
+        <v>6</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B95" s="9">
+        <v>46113</v>
+      </c>
+      <c r="C95" s="3">
+        <v>9</v>
+      </c>
+      <c r="D95" s="3">
+        <v>5</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" s="41" customFormat="1">
+      <c r="A96" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B96" s="40">
+        <v>46114</v>
+      </c>
+      <c r="C96" s="18">
+        <v>9</v>
+      </c>
+      <c r="D96" s="18">
+        <v>5</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="I96" s="20"/>
+      <c r="J96" s="18"/>
+      <c r="K96" s="18"/>
+      <c r="L96" s="18"/>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B97" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C97" s="3">
+        <v>9</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G97" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H97" s="21" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B98" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C98" s="3">
+        <v>9</v>
+      </c>
+      <c r="D98" s="3">
+        <v>2</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G98" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H98" s="21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B99" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C99" s="3">
+        <v>9</v>
+      </c>
+      <c r="D99" s="3">
+        <v>1</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G99" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H99" s="21" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B100" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C100" s="3">
+        <v>9</v>
+      </c>
+      <c r="D100" s="3">
+        <v>1</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G100" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H100" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B101" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C101" s="3">
+        <v>9</v>
+      </c>
+      <c r="D101" s="3">
+        <v>1</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G101" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H101" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B102" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C102" s="3">
+        <v>9</v>
+      </c>
+      <c r="D102" s="3">
+        <v>2</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G102" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H102" s="21" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B103" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C103" s="3">
+        <v>9</v>
+      </c>
+      <c r="D103" s="3">
+        <v>1</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G103" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H103" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B104" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C104" s="3">
+        <v>9</v>
+      </c>
+      <c r="D104" s="3">
+        <v>1</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G104" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H104" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="21">
+      <c r="A105" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B105" s="9">
+        <v>46114</v>
+      </c>
+      <c r="C105" s="3">
+        <v>9</v>
+      </c>
+      <c r="D105" s="3">
+        <v>7</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F105" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="21">
+      <c r="A106" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B106" s="9">
+        <v>46116</v>
+      </c>
+      <c r="C106" s="3">
+        <v>10</v>
+      </c>
+      <c r="D106" s="3">
+        <v>9</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F106" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="21">
+      <c r="A107" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B107" s="9">
+        <v>46117</v>
+      </c>
+      <c r="C107" s="3">
+        <v>10</v>
+      </c>
+      <c r="D107" s="3">
+        <v>8</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F107" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B108" s="9">
+        <v>46118</v>
+      </c>
+      <c r="C108" s="3">
+        <v>10</v>
+      </c>
+      <c r="D108" s="3">
+        <v>6</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B109" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C109" s="3">
+        <v>10</v>
+      </c>
+      <c r="D109" s="3">
+        <v>4</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" s="47" customFormat="1">
+      <c r="A110" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B110" s="45">
+        <v>46120</v>
+      </c>
+      <c r="C110" s="44">
+        <v>10</v>
+      </c>
+      <c r="D110" s="44">
+        <v>24</v>
+      </c>
+      <c r="E110" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="F110" s="44" t="s">
+        <v>347</v>
+      </c>
+      <c r="G110" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="H110" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="I110" s="46"/>
+      <c r="J110" s="44"/>
+      <c r="K110" s="44"/>
+      <c r="L110" s="44"/>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B111" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C111" s="3">
+        <v>10</v>
+      </c>
+      <c r="D111" s="3">
+        <v>1</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H111" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B112" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C112" s="3">
+        <v>10</v>
+      </c>
+      <c r="D112" s="3">
+        <v>1</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H112" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B113" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C113" s="3">
+        <v>10</v>
+      </c>
+      <c r="D113" s="3">
+        <v>1</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H113" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B114" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C114" s="3">
+        <v>10</v>
+      </c>
+      <c r="D114" s="3">
+        <v>1</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H114" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B115" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C115" s="3">
+        <v>10</v>
+      </c>
+      <c r="D115" s="3">
+        <v>1</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H115" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B116" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C116" s="3">
+        <v>10</v>
+      </c>
+      <c r="D116" s="3">
+        <v>1</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H116" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B117" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C117" s="3">
+        <v>10</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H117" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B118" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C118" s="3">
+        <v>10</v>
+      </c>
+      <c r="D118" s="3">
+        <v>1</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H118" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B119" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C119" s="3">
+        <v>10</v>
+      </c>
+      <c r="D119" s="3">
+        <v>1</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H119" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B120" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C120" s="3">
+        <v>10</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H120" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B121" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C121" s="3">
+        <v>10</v>
+      </c>
+      <c r="D121" s="3">
+        <v>1</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H121" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B122" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C122" s="3">
+        <v>10</v>
+      </c>
+      <c r="D122" s="3">
+        <v>1</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H122" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B123" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C123" s="3">
+        <v>10</v>
+      </c>
+      <c r="D123" s="3">
+        <v>2</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H123" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B124" s="9">
+        <v>46120</v>
+      </c>
+      <c r="C124" s="3">
+        <v>10</v>
+      </c>
+      <c r="D124" s="3">
+        <v>1</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H124" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" s="47" customFormat="1">
+      <c r="A125" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B125" s="45">
+        <v>46120</v>
+      </c>
+      <c r="C125" s="44">
+        <v>10</v>
+      </c>
+      <c r="D125" s="44">
+        <v>1</v>
+      </c>
+      <c r="E125" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="F125" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="G125" s="44" t="s">
+        <v>359</v>
+      </c>
+      <c r="H125" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="I125" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="J125" s="44"/>
+      <c r="K125" s="44"/>
+      <c r="L125" s="44"/>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B126" s="9">
+        <v>46121</v>
+      </c>
+      <c r="C126" s="3">
+        <v>10</v>
+      </c>
+      <c r="D126" s="3">
+        <v>6</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B127" s="9">
+        <v>46121</v>
+      </c>
+      <c r="C127" s="3">
+        <v>10</v>
+      </c>
+      <c r="D127" s="3">
+        <v>5</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B128" s="9">
+        <v>46121</v>
+      </c>
+      <c r="C128" s="3">
+        <v>10</v>
+      </c>
+      <c r="D128" s="3">
+        <v>12</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B129" s="9">
+        <v>46122</v>
+      </c>
+      <c r="C129" s="3">
+        <v>10</v>
+      </c>
+      <c r="D129" s="3">
+        <v>28</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I129" s="48"/>
+    </row>
+    <row r="130" spans="1:12" s="41" customFormat="1">
+      <c r="A130" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B130" s="40">
+        <v>46122</v>
+      </c>
+      <c r="C130" s="18">
+        <v>10</v>
+      </c>
+      <c r="D130" s="18">
+        <v>12</v>
+      </c>
+      <c r="E130" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="F130" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="G130" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H130" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="I130" s="20"/>
+      <c r="J130" s="18"/>
+      <c r="K130" s="18"/>
+      <c r="L130" s="18"/>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B131" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C131" s="3">
+        <v>11</v>
+      </c>
+      <c r="D131" s="3">
+        <v>1</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H131" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B132" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C132" s="3">
+        <v>11</v>
+      </c>
+      <c r="D132" s="3">
+        <v>1</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H132" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B133" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C133" s="3">
+        <v>11</v>
+      </c>
+      <c r="D133" s="3">
+        <v>1</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H133" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B134" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C134" s="3">
+        <v>11</v>
+      </c>
+      <c r="D134" s="3">
+        <v>1</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H134" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B135" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C135" s="3">
+        <v>11</v>
+      </c>
+      <c r="D135" s="3">
+        <v>1</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H135" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B136" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C136" s="3">
+        <v>11</v>
+      </c>
+      <c r="D136" s="3">
+        <v>1</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H136" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B137" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C137" s="3">
+        <v>11</v>
+      </c>
+      <c r="D137" s="3">
+        <v>1</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H137" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B138" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C138" s="3">
+        <v>11</v>
+      </c>
+      <c r="D138" s="3">
+        <v>1</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H138" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B139" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C139" s="3">
+        <v>11</v>
+      </c>
+      <c r="D139" s="3">
+        <v>1</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H139" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B140" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C140" s="3">
+        <v>11</v>
+      </c>
+      <c r="D140" s="3">
+        <v>1</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H140" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" s="47" customFormat="1">
+      <c r="A141" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B141" s="45">
+        <v>46126</v>
+      </c>
+      <c r="C141" s="44">
+        <v>11</v>
+      </c>
+      <c r="D141" s="44">
+        <v>1</v>
+      </c>
+      <c r="E141" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="F141" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H141" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="I141" s="44" t="s">
+        <v>393</v>
+      </c>
+      <c r="J141" s="44"/>
+      <c r="K141" s="44"/>
+      <c r="L141" s="44"/>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B142" s="9">
+        <v>46123</v>
+      </c>
+      <c r="C142" s="3">
+        <v>11</v>
+      </c>
+      <c r="D142" s="3">
+        <v>5</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B143" s="9">
+        <v>46123</v>
+      </c>
+      <c r="C143" s="3">
+        <v>11</v>
+      </c>
+      <c r="D143" s="3">
+        <v>5</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B144" s="9">
+        <v>46124</v>
+      </c>
+      <c r="C144" s="3">
+        <v>11</v>
+      </c>
+      <c r="D144" s="3">
+        <v>8</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B145" s="9">
+        <v>46124</v>
+      </c>
+      <c r="C145" s="3">
+        <v>11</v>
+      </c>
+      <c r="D145" s="3">
+        <v>6</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" s="47" customFormat="1">
+      <c r="A146" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B146" s="45">
+        <v>46124</v>
+      </c>
+      <c r="C146" s="44">
+        <v>11</v>
+      </c>
+      <c r="D146" s="44">
+        <v>8</v>
+      </c>
+      <c r="E146" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="F146" s="44" t="s">
+        <v>410</v>
+      </c>
+      <c r="G146" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="H146" s="44" t="s">
+        <v>409</v>
+      </c>
+      <c r="I146" s="46"/>
+      <c r="J146" s="44"/>
+      <c r="K146" s="44"/>
+      <c r="L146" s="44"/>
+    </row>
+    <row r="147" spans="1:12">
+      <c r="A147" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B147" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C147" s="3">
+        <v>11</v>
+      </c>
+      <c r="D147" s="3">
+        <v>8</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
+      <c r="A148" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B148" s="9">
+        <v>46127</v>
+      </c>
+      <c r="C148" s="3">
+        <v>11</v>
+      </c>
+      <c r="D148" s="3">
+        <v>5</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" s="52" customFormat="1">
+      <c r="A149" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B149" s="50">
+        <v>46127</v>
+      </c>
+      <c r="C149" s="49">
+        <v>11</v>
+      </c>
+      <c r="D149" s="49">
+        <v>9</v>
+      </c>
+      <c r="E149" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="F149" s="49" t="s">
+        <v>420</v>
+      </c>
+      <c r="G149" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="H149" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="I149" s="51"/>
+      <c r="J149" s="49"/>
+      <c r="K149" s="49"/>
+      <c r="L149" s="49"/>
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B150" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C150" s="3">
+        <v>12</v>
+      </c>
+      <c r="D150" s="3">
+        <v>1</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H150" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
+      <c r="A151" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B151" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C151" s="3">
+        <v>12</v>
+      </c>
+      <c r="D151" s="3">
+        <v>1</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H151" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B152" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C152" s="3">
+        <v>12</v>
+      </c>
+      <c r="D152" s="3">
+        <v>2</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H152" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B153" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C153" s="3">
+        <v>13</v>
+      </c>
+      <c r="D153" s="3">
+        <v>1</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H153" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
+      <c r="A154" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B154" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C154" s="3">
+        <v>17</v>
+      </c>
+      <c r="D154" s="3">
+        <v>1</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H154" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B155" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C155" s="3">
+        <v>17</v>
+      </c>
+      <c r="D155" s="3">
+        <v>1</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H155" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
+      <c r="A156" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B156" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C156" s="3">
+        <v>12</v>
+      </c>
+      <c r="D156" s="3">
+        <v>1</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H156" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
+      <c r="A157" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B157" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C157" s="3">
+        <v>12</v>
+      </c>
+      <c r="D157" s="3">
+        <v>1</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H157" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
+      <c r="A158" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B158" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C158" s="3">
+        <v>12</v>
+      </c>
+      <c r="D158" s="3">
+        <v>1</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H158" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" s="47" customFormat="1">
+      <c r="A159" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B159" s="45">
+        <v>46132</v>
+      </c>
+      <c r="C159" s="44">
+        <v>12</v>
+      </c>
+      <c r="D159" s="44">
+        <v>1</v>
+      </c>
+      <c r="E159" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="F159" s="44" t="s">
+        <v>439</v>
+      </c>
+      <c r="G159" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H159" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="I159" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="J159" s="44"/>
+      <c r="K159" s="44"/>
+      <c r="L159" s="44"/>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B160" s="9">
+        <v>46128</v>
+      </c>
+      <c r="C160" s="3">
+        <v>11</v>
+      </c>
+      <c r="D160" s="3">
+        <v>6</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="A161" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="9">
+        <v>46129</v>
+      </c>
+      <c r="C161" s="3">
+        <v>11</v>
+      </c>
+      <c r="D161" s="3">
+        <v>8</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B162" s="9">
+        <v>46129</v>
+      </c>
+      <c r="C162" s="3">
+        <v>11</v>
+      </c>
+      <c r="D162" s="3">
+        <v>8</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B163" s="9">
+        <v>46131</v>
+      </c>
+      <c r="C163" s="3">
+        <v>11</v>
+      </c>
+      <c r="D163" s="3">
+        <v>6</v>
+      </c>
+      <c r="E163" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="I163" s="21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B164" s="9">
+        <v>46131</v>
+      </c>
+      <c r="C164" s="3">
+        <v>11</v>
+      </c>
+      <c r="D164" s="3">
+        <v>6</v>
+      </c>
+      <c r="E164" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="I164" s="21" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B165" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C165" s="3">
+        <v>12</v>
+      </c>
+      <c r="D165" s="3">
+        <v>12</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B166" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C166" s="3">
+        <v>12</v>
+      </c>
+      <c r="D166" s="3">
+        <v>6</v>
+      </c>
+      <c r="E166" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B167" s="9">
+        <v>46132</v>
+      </c>
+      <c r="C167" s="3">
+        <v>12</v>
+      </c>
+      <c r="D167" s="3">
+        <v>9</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" s="47" customFormat="1">
+      <c r="A168" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B168" s="45">
+        <v>46132</v>
+      </c>
+      <c r="C168" s="44">
+        <v>12</v>
+      </c>
+      <c r="D168" s="44">
+        <v>8</v>
+      </c>
+      <c r="E168" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="F168" s="44" t="s">
+        <v>459</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H168" s="44" t="s">
+        <v>460</v>
+      </c>
+      <c r="I168" s="46"/>
+      <c r="J168" s="44"/>
+      <c r="K168" s="44"/>
+      <c r="L168" s="44"/>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B169" s="45">
+        <v>46135</v>
+      </c>
+      <c r="C169" s="3">
+        <v>12</v>
+      </c>
+      <c r="D169" s="3">
+        <v>6</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B170" s="45">
+        <v>46135</v>
+      </c>
+      <c r="C170" s="3">
+        <v>12</v>
+      </c>
+      <c r="D170" s="3">
+        <v>13</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" s="47" customFormat="1" ht="21">
+      <c r="A171" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B171" s="45">
+        <v>46136</v>
+      </c>
+      <c r="C171" s="44">
+        <v>12</v>
+      </c>
+      <c r="D171" s="44">
+        <v>6</v>
+      </c>
+      <c r="E171" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F171" s="56" t="s">
+        <v>467</v>
+      </c>
+      <c r="G171" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="H171" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="I171" s="46"/>
+      <c r="J171" s="44"/>
+      <c r="K171" s="44"/>
+      <c r="L171" s="44"/>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="A172" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B172" s="9">
+        <v>46137</v>
+      </c>
+      <c r="C172" s="3">
+        <v>13</v>
+      </c>
+      <c r="D172" s="3">
+        <v>8</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="A173" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B173" s="9">
+        <v>46138</v>
+      </c>
+      <c r="C173" s="3">
+        <v>13</v>
+      </c>
+      <c r="D173" s="3">
+        <v>6</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="A174" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B174" s="9">
+        <v>46138</v>
+      </c>
+      <c r="C174" s="3">
+        <v>13</v>
+      </c>
+      <c r="D174" s="3">
+        <v>10</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="A175" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B175" s="9">
+        <v>46138</v>
+      </c>
+      <c r="C175" s="3">
+        <v>13</v>
+      </c>
+      <c r="D175" s="3">
+        <v>10</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="A176" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B176" s="9">
+        <v>46138</v>
+      </c>
+      <c r="C176" s="3">
+        <v>13</v>
+      </c>
+      <c r="D176" s="3">
+        <v>6</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B177" s="9">
+        <v>46138</v>
+      </c>
+      <c r="C177" s="3">
+        <v>13</v>
+      </c>
+      <c r="D177" s="3">
+        <v>16</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" s="47" customFormat="1">
+      <c r="A178" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B178" s="45">
+        <v>46139</v>
+      </c>
+      <c r="C178" s="44">
+        <v>13</v>
+      </c>
+      <c r="D178" s="44">
+        <v>4</v>
+      </c>
+      <c r="E178" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="F178" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="G178" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="H178" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="I178" s="46"/>
+      <c r="J178" s="44"/>
+      <c r="K178" s="44"/>
+      <c r="L178" s="44"/>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B179" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C179" s="3">
+        <v>13</v>
+      </c>
+      <c r="D179" s="3">
+        <v>2</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H179" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B180" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C180" s="3">
+        <v>13</v>
+      </c>
+      <c r="D180" s="3">
+        <v>1</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H180" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B181" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C181" s="3">
+        <v>13</v>
+      </c>
+      <c r="D181" s="3">
+        <v>1</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H181" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="A182" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B182" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C182" s="3">
+        <v>13</v>
+      </c>
+      <c r="D182" s="3">
+        <v>1</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H182" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="A183" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B183" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C183" s="3">
+        <v>13</v>
+      </c>
+      <c r="D183" s="3">
+        <v>1</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H183" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="A184" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B184" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C184" s="3">
+        <v>13</v>
+      </c>
+      <c r="D184" s="3">
+        <v>1</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H184" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="A185" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B185" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C185" s="3">
+        <v>13</v>
+      </c>
+      <c r="D185" s="3">
+        <v>1</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H185" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="A186" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B186" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C186" s="3">
+        <v>13</v>
+      </c>
+      <c r="D186" s="3">
+        <v>1</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H186" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="A187" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B187" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C187" s="3">
+        <v>13</v>
+      </c>
+      <c r="D187" s="3">
+        <v>1</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H187" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12">
+      <c r="A188" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B188" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C188" s="3">
+        <v>13</v>
+      </c>
+      <c r="D188" s="3">
+        <v>1</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H188" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12">
+      <c r="A189" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B189" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C189" s="3">
+        <v>13</v>
+      </c>
+      <c r="D189" s="3">
+        <v>2</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H189" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" s="41" customFormat="1">
+      <c r="A190" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B190" s="40">
+        <v>46140</v>
+      </c>
+      <c r="C190" s="18">
+        <v>13</v>
+      </c>
+      <c r="D190" s="18">
+        <v>1</v>
+      </c>
+      <c r="E190" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="F190" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="G190" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H190" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="I190" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="J190" s="18"/>
+      <c r="K190" s="18"/>
+      <c r="L190" s="18"/>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B191" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C191" s="3">
+        <v>14</v>
+      </c>
+      <c r="D191" s="3">
+        <v>1</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H191" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12">
+      <c r="A192" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B192" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C192" s="3">
+        <v>14</v>
+      </c>
+      <c r="D192" s="3">
+        <v>1</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H192" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12">
+      <c r="A193" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B193" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C193" s="3">
+        <v>14</v>
+      </c>
+      <c r="D193" s="3">
+        <v>2</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H193" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12">
+      <c r="A194" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B194" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C194" s="3">
+        <v>14</v>
+      </c>
+      <c r="D194" s="3">
+        <v>1</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H194" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12">
+      <c r="A195" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B195" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C195" s="3">
+        <v>14</v>
+      </c>
+      <c r="D195" s="3">
+        <v>1</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H195" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12">
+      <c r="A196" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B196" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C196" s="3">
+        <v>14</v>
+      </c>
+      <c r="D196" s="3">
+        <v>1</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H196" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12">
+      <c r="A197" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B197" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C197" s="3">
+        <v>14</v>
+      </c>
+      <c r="D197" s="3">
+        <v>1</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H197" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12">
+      <c r="A198" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B198" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C198" s="3">
+        <v>14</v>
+      </c>
+      <c r="D198" s="3">
+        <v>1</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H198" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12">
+      <c r="A199" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B199" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C199" s="3">
+        <v>14</v>
+      </c>
+      <c r="D199" s="3">
+        <v>1</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H199" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12">
+      <c r="A200" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B200" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C200" s="3">
+        <v>14</v>
+      </c>
+      <c r="D200" s="3">
+        <v>1</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H200" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
+      <c r="A201" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B201" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C201" s="3">
+        <v>14</v>
+      </c>
+      <c r="D201" s="3">
+        <v>1</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H201" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12">
+      <c r="A202" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B202" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C202" s="3">
+        <v>14</v>
+      </c>
+      <c r="D202" s="3">
+        <v>2</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H202" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12">
+      <c r="A203" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B203" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C203" s="3">
+        <v>14</v>
+      </c>
+      <c r="D203" s="3">
+        <v>1</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H203" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" s="47" customFormat="1">
+      <c r="A204" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B204" s="45">
+        <v>46142</v>
+      </c>
+      <c r="C204" s="44">
+        <v>14</v>
+      </c>
+      <c r="D204" s="44">
+        <v>1</v>
+      </c>
+      <c r="E204" s="44" t="s">
+        <v>512</v>
+      </c>
+      <c r="F204" s="44" t="s">
+        <v>533</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H204" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="I204" s="44" t="s">
+        <v>511</v>
+      </c>
+      <c r="K204" s="44"/>
+      <c r="L204" s="44"/>
+    </row>
+    <row r="205" spans="1:12">
+      <c r="A205" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B205" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C205" s="3">
+        <v>14</v>
+      </c>
+      <c r="D205" s="3">
+        <v>25</v>
+      </c>
+      <c r="E205" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12">
+      <c r="A206" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B206" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C206" s="3">
+        <v>14</v>
+      </c>
+      <c r="D206" s="3">
+        <v>6</v>
+      </c>
+      <c r="E206" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="I206" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12">
+      <c r="A207" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B207" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C207" s="3">
+        <v>14</v>
+      </c>
+      <c r="D207" s="3">
+        <v>12</v>
+      </c>
+      <c r="E207" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="I207" s="21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12">
+      <c r="A208" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B208" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C208" s="3">
+        <v>14</v>
+      </c>
+      <c r="D208" s="3">
+        <v>24</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" s="47" customFormat="1">
+      <c r="A209" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B209" s="9">
+        <v>46142</v>
+      </c>
+      <c r="C209" s="44">
+        <v>14</v>
+      </c>
+      <c r="D209" s="44">
+        <v>5</v>
+      </c>
+      <c r="E209" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="F209" s="44" t="s">
+        <v>516</v>
+      </c>
+      <c r="G209" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="H209" s="44" t="s">
+        <v>522</v>
+      </c>
+      <c r="I209" s="46"/>
+      <c r="J209" s="44"/>
+      <c r="K209" s="44"/>
+      <c r="L209" s="44"/>
+    </row>
+    <row r="210" spans="1:12">
+      <c r="A210" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B210" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C210" s="3">
+        <v>15</v>
+      </c>
+      <c r="D210" s="3">
+        <v>1</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H210" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12">
+      <c r="A211" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B211" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C211" s="3">
+        <v>15</v>
+      </c>
+      <c r="D211" s="3">
+        <v>1</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H211" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12">
+      <c r="A212" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B212" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C212" s="3">
+        <v>15</v>
+      </c>
+      <c r="D212" s="3">
+        <v>1</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H212" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12">
+      <c r="A213" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B213" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C213" s="3">
+        <v>15</v>
+      </c>
+      <c r="D213" s="3">
+        <v>1</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H213" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12">
+      <c r="A214" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B214" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C214" s="3">
+        <v>15</v>
+      </c>
+      <c r="D214" s="3">
+        <v>2</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H214" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12">
+      <c r="A215" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B215" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C215" s="3">
+        <v>15</v>
+      </c>
+      <c r="D215" s="3">
+        <v>1</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H215" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12">
+      <c r="A216" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B216" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C216" s="3">
+        <v>15</v>
+      </c>
+      <c r="D216" s="3">
+        <v>1</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H216" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12">
+      <c r="A217" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B217" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C217" s="3">
+        <v>15</v>
+      </c>
+      <c r="D217" s="3">
+        <v>1</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H217" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12">
+      <c r="A218" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B218" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C218" s="3">
+        <v>15</v>
+      </c>
+      <c r="D218" s="3">
+        <v>1</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H218" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12">
+      <c r="A219" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B219" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C219" s="3">
+        <v>15</v>
+      </c>
+      <c r="D219" s="3">
+        <v>1</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H219" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12">
+      <c r="A220" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B220" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C220" s="3">
+        <v>15</v>
+      </c>
+      <c r="D220" s="3">
+        <v>1</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H220" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12">
+      <c r="A221" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B221" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C221" s="3">
+        <v>15</v>
+      </c>
+      <c r="D221" s="3">
+        <v>1</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H221" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12">
+      <c r="A222" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B222" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C222" s="3">
+        <v>15</v>
+      </c>
+      <c r="D222" s="3">
+        <v>1</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H222" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" s="47" customFormat="1">
+      <c r="A223" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B223" s="45">
+        <v>46147</v>
+      </c>
+      <c r="C223" s="44">
+        <v>15</v>
+      </c>
+      <c r="D223" s="44">
+        <v>1</v>
+      </c>
+      <c r="E223" s="44" t="s">
+        <v>548</v>
+      </c>
+      <c r="F223" s="44" t="s">
+        <v>560</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H223" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="I223" s="44" t="s">
+        <v>544</v>
+      </c>
+      <c r="J223" s="44"/>
+      <c r="K223" s="44"/>
+      <c r="L223" s="44"/>
+    </row>
+    <row r="224" spans="1:12">
+      <c r="A224" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B224" s="9">
+        <v>46146</v>
+      </c>
+      <c r="C224" s="3">
+        <v>15</v>
+      </c>
+      <c r="D224" s="3">
+        <v>28</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" s="41" customFormat="1">
+      <c r="A225" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B225" s="40">
+        <v>46146</v>
+      </c>
+      <c r="C225" s="18">
+        <v>15</v>
+      </c>
+      <c r="D225" s="18">
+        <v>20</v>
+      </c>
+      <c r="E225" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F225" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="G225" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H225" s="18" t="s">
+        <v>567</v>
+      </c>
+      <c r="I225" s="20"/>
+      <c r="J225" s="18"/>
+      <c r="K225" s="18"/>
+      <c r="L225" s="18"/>
+    </row>
+    <row r="226" spans="1:12">
+      <c r="A226" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B226" s="40">
+        <v>46147</v>
+      </c>
+      <c r="C226" s="3">
+        <v>15</v>
+      </c>
+      <c r="D226" s="3">
+        <v>6</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12">
+      <c r="A227" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B227" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C227" s="3">
+        <v>16</v>
+      </c>
+      <c r="D227" s="3">
+        <v>1</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H227" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12">
+      <c r="A228" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B228" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C228" s="3">
+        <v>16</v>
+      </c>
+      <c r="D228" s="3">
+        <v>1</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H228" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12">
+      <c r="A229" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B229" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C229" s="3">
+        <v>16</v>
+      </c>
+      <c r="D229" s="3">
+        <v>1</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H229" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12">
+      <c r="A230" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B230" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C230" s="3">
+        <v>16</v>
+      </c>
+      <c r="D230" s="3">
+        <v>1</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H230" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12">
+      <c r="A231" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B231" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C231" s="3">
+        <v>16</v>
+      </c>
+      <c r="D231" s="3">
+        <v>1</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H231" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12">
+      <c r="A232" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B232" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C232" s="3">
+        <v>16</v>
+      </c>
+      <c r="D232" s="3">
+        <v>1</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H232" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12">
+      <c r="A233" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B233" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C233" s="3">
+        <v>16</v>
+      </c>
+      <c r="D233" s="3">
+        <v>1</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H233" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12">
+      <c r="A234" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B234" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C234" s="3">
+        <v>16</v>
+      </c>
+      <c r="D234" s="3">
+        <v>1</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H234" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12">
+      <c r="A235" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B235" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C235" s="3">
+        <v>16</v>
+      </c>
+      <c r="D235" s="3">
+        <v>1</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H235" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12">
+      <c r="A236" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B236" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C236" s="3">
+        <v>16</v>
+      </c>
+      <c r="D236" s="3">
+        <v>1</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H236" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12">
+      <c r="A237" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B237" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C237" s="3">
+        <v>16</v>
+      </c>
+      <c r="D237" s="3">
+        <v>1</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H237" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12">
+      <c r="A238" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B238" s="59">
+        <v>46150</v>
+      </c>
+      <c r="C238" s="3">
+        <v>16</v>
+      </c>
+      <c r="D238" s="3">
+        <v>1</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H238" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" s="47" customFormat="1">
+      <c r="A239" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B239" s="45">
+        <v>46150</v>
+      </c>
+      <c r="C239" s="44">
+        <v>16</v>
+      </c>
+      <c r="D239" s="44">
+        <v>1</v>
+      </c>
+      <c r="E239" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="F239" s="44" t="s">
+        <v>587</v>
+      </c>
+      <c r="G239" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H239" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="I239" s="44" t="s">
+        <v>575</v>
+      </c>
+      <c r="J239" s="44"/>
+      <c r="K239" s="44"/>
+      <c r="L239" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
@@ -2606,17 +10419,32 @@
     <hyperlink ref="J21" r:id="rId2" xr:uid="{856784B2-DF93-5747-A307-E44064091B65}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DA70E8C-358E-6B45-BD21-EC9E1B8B9C46}">
+          <x14:formula1>
+            <xm:f>ドロップダウンリスト!$A$1:$A$42</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E55 E57:E58 E71:E74 E60:E69 E76:E77 E82:E87 E124 E90:E120 E122 E126:E135 E137:E138 E140:E146 E148:E156 E159:E162 E167 E165 E169:E204 E208:E214 E222 E224:E230 E232:E267</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B216AA4-6808-5C47-AC72-4A2D3BCCB154}">
-  <dimension ref="A2:D9"/>
+  <sheetPr>
+    <tabColor theme="5" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A2:D42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="55.85546875" customWidth="1"/>
+    <col min="3" max="3" width="63" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" s="11" customFormat="1">
@@ -2624,7 +10452,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>13</v>
@@ -2632,83 +10460,445 @@
       <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" s="11" customFormat="1" ht="42">
-      <c r="A3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>55</v>
+      <c r="A3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="A4" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="63">
+      <c r="A6" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="21">
+      <c r="A7" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="63">
-      <c r="A6" s="12" t="s">
+      <c r="C7" s="55" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="21">
+      <c r="A8" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="63">
+      <c r="A9" s="47" t="s">
+        <v>445</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="42">
+      <c r="A10" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="63">
+      <c r="A11" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="21">
+      <c r="A12" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="63">
+      <c r="A13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="63">
-      <c r="A7" s="13" t="s">
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="63">
-      <c r="A8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" t="s">
-        <v>107</v>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="57"/>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="84">
+      <c r="A17" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="63">
+      <c r="A18" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="63">
+      <c r="A19" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="21">
+      <c r="A20" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="21">
+      <c r="A21" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="21">
+      <c r="A22" t="s">
+        <v>213</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="21">
+      <c r="A23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="21">
+      <c r="A24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="21">
+      <c r="A25" t="s">
+        <v>265</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" s="57" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="21">
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="21">
+      <c r="A28" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="63">
+      <c r="A29" t="s">
+        <v>299</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="63">
+      <c r="A30" t="s">
+        <v>309</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="42">
+      <c r="A31" t="s">
+        <v>517</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="42">
+      <c r="A32" t="s">
+        <v>329</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="42">
+      <c r="A33" t="s">
+        <v>332</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="63">
+      <c r="A34" t="s">
+        <v>380</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C35" s="48" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="84">
+      <c r="A36" t="s">
+        <v>386</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="84">
+      <c r="A37" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="21">
+      <c r="A38" t="s">
+        <v>468</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="63">
+      <c r="A39" t="s">
+        <v>480</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="42">
+      <c r="A40" t="s">
+        <v>520</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="42">
+      <c r="A41" s="47" t="s">
+        <v>564</v>
+      </c>
+      <c r="B41" t="s">
+        <v>384</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="84">
+      <c r="A42" s="47" t="s">
+        <v>565</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+  </mergeCells>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2716,7 +10906,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0FD45A-19BE-8A4E-80AC-10371E568E16}">
-  <dimension ref="A2:B8"/>
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A2:B52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -2724,53 +10917,266 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2">
-      <c r="A2" s="17" t="s">
-        <v>57</v>
+      <c r="A2" s="13" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>59</v>
+        <v>49</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>65</v>
+        <v>57</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>61</v>
+        <v>51</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="B7" s="18" t="s">
-        <v>64</v>
+      <c r="B7" s="14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="29" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" s="29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" s="29" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" s="29" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" s="29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="29" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="29" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="29" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="29" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="29" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="29" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="29" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="29" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2784,4 +11190,231 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D7EA7C9-7E11-4F41-834D-B073514E6168}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:A42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="29" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="29" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="29" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="29" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="29" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="29" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="29" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="29" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="29" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="29" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="29" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>